--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_206_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_206_R21.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9397</v>
+        <v>4.0859</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0836</v>
+        <v>2.0189</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8561</v>
+        <v>2.0669</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3259</v>
+        <v>1.4134</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.059</v>
+        <v>0.7911</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3849</v>
+        <v>0.6223</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0672</v>
+        <v>1.4319</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1408</v>
+        <v>1.4354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0736</v>
+        <v>-0.0035</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3931</v>
+        <v>-0.0185</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0818</v>
+        <v>-0.6443</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3113</v>
+        <v>0.6258</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>3.0597</v>
+        <v>-0.3844</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8467</v>
+        <v>-0.2199</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2131</v>
+        <v>-0.1645</v>
       </c>
       <c r="V2" t="n">
+        <v>3.7527</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.3584</v>
+      </c>
+      <c r="X2" t="n">
         <v>0.3943</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.5361</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-0.1418</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5419</v>
+        <v>3.9027</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0572</v>
+        <v>2.8213</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4847</v>
+        <v>1.0814</v>
       </c>
       <c r="G3" t="n">
         <v>1.9332</v>
@@ -688,13 +688,13 @@
         <v>0.4639</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6783</v>
+        <v>0.0391</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4876</v>
+        <v>0.2517</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1907</v>
+        <v>-0.2126</v>
       </c>
       <c r="V3" t="n">
         <v>1.4665</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9577</v>
+        <v>2.8008</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1933</v>
+        <v>1.3144</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7645</v>
+        <v>1.4864</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4134</v>
+        <v>0.3259</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7911</v>
+        <v>-0.059</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6223</v>
+        <v>0.3849</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4319</v>
+        <v>-0.0672</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4354</v>
+        <v>-0.1408</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0035</v>
+        <v>0.0736</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0185</v>
+        <v>0.3931</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6443</v>
+        <v>0.0818</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6258</v>
+        <v>0.3113</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5125</v>
+        <v>0.9208</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0455</v>
+        <v>1.0774</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.467</v>
+        <v>-0.1566</v>
       </c>
       <c r="V4" t="n">
-        <v>3.7527</v>
+        <v>0.3943</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3584</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2455</v>
+        <v>2.0946</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6439</v>
+        <v>0.7618</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6016</v>
+        <v>1.3328</v>
       </c>
       <c r="G5" t="n">
         <v>0.9742</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3435</v>
+        <v>0.1926</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6423</v>
+        <v>0.3734</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5703</v>
+        <v>1.8391</v>
       </c>
       <c r="E6" t="n">
         <v>1.1175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4527</v>
+        <v>0.7216</v>
       </c>
       <c r="G6" t="n">
         <v>1.6151</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9726</v>
+        <v>-0.7038</v>
       </c>
       <c r="T6" t="n">
         <v>-0.3655</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6071</v>
+        <v>-0.3383</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4251</v>
+        <v>1.0904</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7507</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3256</v>
+        <v>0.222</v>
       </c>
       <c r="G7" t="n">
-        <v>0.728</v>
+        <v>0.3333</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4636</v>
+        <v>1.5245</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2644</v>
+        <v>-1.1912</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8498</v>
+        <v>0.4983</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7393999999999999</v>
+        <v>2.158</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1104</v>
+        <v>-1.6597</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1219</v>
+        <v>-0.165</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2759</v>
+        <v>-0.6335</v>
       </c>
       <c r="O7" t="n">
-        <v>0.154</v>
+        <v>0.4685</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6818</v>
+        <v>-0.011</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7591</v>
+        <v>0.1535</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.1645</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2862</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3655</v>
+        <v>0.1915</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0427</v>
+        <v>-1.301</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3228</v>
+        <v>1.4925</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3333</v>
+        <v>1.3071</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5245</v>
+        <v>1.7154</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1912</v>
+        <v>-0.4082</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4983</v>
+        <v>0.1456</v>
       </c>
       <c r="K8" t="n">
-        <v>2.158</v>
+        <v>1.1294</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.6597</v>
+        <v>-0.9838</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.165</v>
+        <v>1.1615</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6335</v>
+        <v>0.586</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4685</v>
+        <v>0.5756</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7358</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>-0.2869</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.06370000000000001</v>
+        <v>-0.3648</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3468</v>
+        <v>-0.3333</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5369</v>
+        <v>0.9251</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1901</v>
+        <v>-1.2584</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3071</v>
+        <v>0.728</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7154</v>
+        <v>0.4636</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4082</v>
+        <v>0.2644</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1456</v>
+        <v>0.8498</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1294</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9838</v>
+        <v>0.1104</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1615</v>
+        <v>-0.1219</v>
       </c>
       <c r="N9" t="n">
-        <v>0.586</v>
+        <v>-0.2759</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5756</v>
+        <v>0.154</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1901</v>
+        <v>-0.0767</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5228</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6673</v>
+        <v>-0.0101</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3175</v>
+        <v>-1.3004</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1173</v>
+        <v>-2.9994</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7998</v>
+        <v>1.699</v>
       </c>
       <c r="G10" t="n">
         <v>1.165</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8615</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8883</v>
+        <v>-0.7703</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0268</v>
+        <v>-0.074</v>
       </c>
       <c r="V10" t="n">
         <v>0.9304</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3143</v>
+        <v>-1.8088</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4209</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8934</v>
+        <v>-0.8598</v>
       </c>
       <c r="G11" t="n">
         <v>1.0041</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3905</v>
+        <v>0.1149</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2987</v>
+        <v>0.1731</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.0582</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9651</v>
+        <v>-2.6284</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0971</v>
+        <v>-3.8612</v>
       </c>
       <c r="F12" t="n">
-        <v>1.132</v>
+        <v>1.2328</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1045</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0925</v>
+        <v>-0.7558</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1123</v>
+        <v>-0.8764</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0198</v>
+        <v>0.1206</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3898</v>
+        <v>-5.2218</v>
       </c>
       <c r="E13" t="n">
         <v>-5.4952</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1054</v>
+        <v>0.2735</v>
       </c>
       <c r="G13" t="n">
         <v>-3.1363</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4854</v>
+        <v>-0.3174</v>
       </c>
       <c r="T13" t="n">
         <v>-0.4402</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7122</v>
+        <v>4.712300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.778499999999999</v>
+        <v>-4.7785</v>
       </c>
       <c r="F14" t="n">
         <v>9.490699999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>5.558499999999997</v>
+        <v>5.5585</v>
       </c>
       <c r="H14" t="n">
         <v>5.558299999999999</v>
@@ -1528,7 +1528,7 @@
         <v>-3.3802</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5677999999999996</v>
+        <v>0.5678000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-2.8125</v>
@@ -1546,13 +1546,13 @@
         <v>13.9172</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.4776</v>
+        <v>-2.4777</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5507</v>
+        <v>-1.5509</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9267</v>
+        <v>-0.9268000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.7912</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.279</v>
+        <v>4.7071</v>
       </c>
       <c r="E15" t="n">
-        <v>2.521</v>
+        <v>2.2851</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7581</v>
+        <v>2.422</v>
       </c>
       <c r="G15" t="n">
         <v>2.0443</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3249</v>
+        <v>0.753</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4683</v>
+        <v>0.2324</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8566</v>
+        <v>0.5206</v>
       </c>
       <c r="V15" t="n">
         <v>1.214</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6159</v>
+        <v>2.8068</v>
       </c>
       <c r="E16" t="n">
         <v>0.8093</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8067</v>
+        <v>1.9975</v>
       </c>
       <c r="G16" t="n">
         <v>2.8328</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1937</v>
+        <v>-0.0029</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3927</v>
       </c>
       <c r="U16" t="n">
-        <v>0.199</v>
+        <v>0.3899</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1829</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.823</v>
+        <v>0.4614</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8389</v>
+        <v>0.1974</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0159</v>
+        <v>0.264</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4065</v>
+        <v>0.4629</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6341</v>
+        <v>-0.3301</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2276</v>
+        <v>0.793</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6589</v>
+        <v>0.5528</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5853</v>
+        <v>0.1246</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0736</v>
+        <v>0.4282</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0655</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2195</v>
+        <v>-0.4547</v>
       </c>
       <c r="O17" t="n">
-        <v>0.154</v>
+        <v>0.3648</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2811</v>
+        <v>0.0011</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2675</v>
+        <v>-0.0154</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0136</v>
+        <v>0.0165</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8197</v>
+        <v>-0.9304</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0.8197</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8919</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1355</v>
+        <v>0.1573</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9051</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2304</v>
+        <v>0.1573</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4629</v>
+        <v>0.1573</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3301</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.793</v>
+        <v>0.1573</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5528</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1246</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4282</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.1573</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4547</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3648</v>
+        <v>0.1573</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6752</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6923</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0171</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1573</v>
+        <v>0.0251</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.7157</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1573</v>
+        <v>-1.6906</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1573</v>
+        <v>-0.4065</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.6341</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1573</v>
+        <v>0.2276</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.6589</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5853</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1573</v>
+        <v>-1.0655</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.2195</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1573</v>
+        <v>0.154</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.4833</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.1444</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.3389</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.8197</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1208</v>
+        <v>-0.4467</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9694</v>
+        <v>-0.2616</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1514</v>
+        <v>-0.1851</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0262</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2544</v>
+        <v>0.4197</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2908</v>
+        <v>0.4169</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5544</v>
+        <v>-0.7738</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9885</v>
+        <v>-1.3987</v>
       </c>
       <c r="F21" t="n">
-        <v>0.434</v>
+        <v>0.6249</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1055</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4336</v>
+        <v>0.347</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>-0.2985</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4547</v>
+        <v>0.6456</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9288</v>
+        <v>-1.0473</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0413</v>
+        <v>-1.4515</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1125</v>
+        <v>0.4042</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2558</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.673</v>
+        <v>0.2084</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>0.1417</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2249</v>
+        <v>0.0668</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1685</v>
+        <v>-2.9498</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.7615</v>
+        <v>-4.6436</v>
       </c>
       <c r="F23" t="n">
-        <v>1.593</v>
+        <v>1.6938</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5715</v>
@@ -2248,13 +2248,13 @@
         <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1331</v>
+        <v>0.0857</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1608</v>
+        <v>-0.0428</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0277</v>
+        <v>0.1285</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.535</v>
+        <v>-2.9902</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9798</v>
+        <v>-2.6259</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5552</v>
+        <v>-0.3643</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0984</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5241</v>
+        <v>0.0206</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1401</v>
+        <v>0.331</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4154</v>
+        <v>-3.8757</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8245</v>
+        <v>-4.1168</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4091</v>
+        <v>0.2411</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5917</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5917</v>
+        <v>-0.0521</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6563</v>
+        <v>0.0514</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0646</v>
+        <v>-0.1034</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.712199999999999</v>
+        <v>-3.925800000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.4907</v>
+        <v>-9.490600000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>4.778599999999999</v>
+        <v>5.5648</v>
       </c>
       <c r="G26" t="n">
         <v>-5.558299999999999</v>
@@ -2452,10 +2452,10 @@
         <v>-5.5583</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5675999999999994</v>
+        <v>-0.5676000000000003</v>
       </c>
       <c r="K26" t="n">
         <v>2.8125</v>
@@ -2473,7 +2473,7 @@
         <v>3.3804</v>
       </c>
       <c r="P26" t="n">
-        <v>1.159799999999999</v>
+        <v>1.1598</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.9173</v>
@@ -2482,13 +2482,13 @@
         <v>15.077</v>
       </c>
       <c r="S26" t="n">
-        <v>2.4776</v>
+        <v>3.2638</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9268999999999997</v>
+        <v>0.9270000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5508</v>
+        <v>2.337299999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-2.7912</v>
